--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市番禺区番禺万达</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
+          <t>前进街道黄埔大道东663号</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米汽车广东省广州市番禺区番禺万达</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号</t>
+          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市溧阳市上河城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>上河城F1层</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>江苏省常州市新北区顺园路88-30号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
+          <t>小米汽车江苏省常州市溧阳市上河城</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区顺园路88-30号</t>
+          <t>上河城F1层</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>上海陆家嘴中心品牌体验店</t>
+          <t>上海环球港品牌体验店</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
+          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海陆家嘴中心品牌体验店</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海环球港品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,29 +16616,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,29 +16712,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,29 +16968,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -17012,17 +17012,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,29 +17064,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17204,17 +17204,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17263,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17327,22 +17327,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎城购物公园负一层 KFC 门口</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>瑞鼎城购物公园负一层 KFC 门口</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市溧阳市上河城</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>上河城F1层</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市溧阳市上河城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>上河城F1层</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
+          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区盛泽天虹商场</t>
+          <t>乌盆港路150号</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
+          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>乌盆港路150号</t>
+          <t>江苏省苏州市吴江区盛泽天虹商场</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
@@ -16628,17 +16628,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,29 +16968,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,29 +17000,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,29 +17032,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,29 +17064,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17135,22 +17135,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17199,7 +17199,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -17209,12 +17209,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17236,17 +17236,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17263,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17396,17 +17396,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17519,22 +17519,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17556,17 +17556,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,29 +17576,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米汽车广东省广州市番禺区番禺万达</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号</t>
+          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市番禺区番禺万达</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
+          <t>前进街道黄埔大道东663号</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区顺园路88-30号</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>江苏省常州市新北区顺园路88-30号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
+          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>乌盆港路150号</t>
+          <t>江苏省苏州市吴江区盛泽天虹商场</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
+          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区盛泽天虹商场</t>
+          <t>乌盆港路150号</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>上海环球港品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海环球港品牌体验店</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>成都天府公园111体验店</t>
+          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
+          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
+          <t>成都天府公园111体验店</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
+          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,29 +16520,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16628,17 +16628,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16729,12 +16729,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,29 +16904,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,29 +17000,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,29 +17032,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17135,22 +17135,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17263,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17300,17 +17300,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17327,22 +17327,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17391,22 +17391,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17524,17 +17524,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,29 +17544,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,29 +17576,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市莱芜区茂业天地</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>茂业天地购物中心1楼</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市莱芜区茂业天地</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>茂业天地购物中心1楼</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市番禺区番禺万达</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
+          <t>前进街道黄埔大道东663号</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米汽车广东省广州市番禺区番禺万达</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号</t>
+          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市溧阳市上河城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>上河城F1层</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市溧阳市上河城</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>上河城F1层</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海陆家嘴中心品牌体验店</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>上海陆家嘴中心品牌体验店</t>
+          <t>上海环球港品牌体验店</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
+          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海环球港品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,29 +16520,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,29 +16616,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,29 +16904,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,29 +16968,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -17012,17 +17012,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17140,17 +17140,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17268,17 +17268,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17300,17 +17300,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17327,22 +17327,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17359,7 +17359,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -17369,12 +17369,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17391,22 +17391,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,29 +17512,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,29 +17544,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>瑞鼎城购物公园负一层 KFC 门口</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎城购物公园负一层 KFC 门口</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>江苏省常州市新北区顺园路88-30号</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市溧阳市上河城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>上河城F1层</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
+          <t>小米汽车江苏省常州市溧阳市上河城</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区顺园路88-30号</t>
+          <t>上河城F1层</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>上海环球港品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海环球港品牌体验店</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
+          <t>成都天府公园111体验店</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
+          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>成都天府公园111体验店</t>
+          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
+          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,29 +16616,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,29 +16680,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,29 +16904,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,29 +16968,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -17012,17 +17012,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17140,17 +17140,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17268,17 +17268,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17327,22 +17327,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17359,22 +17359,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17396,17 +17396,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -17556,17 +17556,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17588,17 +17588,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>瑞鼎城购物公园负一层 KFC 门口</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎城购物公园负一层 KFC 门口</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,12 +11191,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>上海陆家嘴中心品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海陆家嘴中心品牌体验店</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -16537,12 +16537,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,29 +16616,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,29 +16680,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,29 +16744,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,29 +16904,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16953,12 +16953,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -17012,17 +17012,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -17103,22 +17103,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17204,17 +17204,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17236,17 +17236,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17268,17 +17268,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17359,22 +17359,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17391,22 +17391,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,29 +17512,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17556,17 +17556,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,29 +17576,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市莱芜区茂业天地</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>茂业天地购物中心1楼</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东省济南市莱芜区茂业天地</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>茂业天地购物中心1楼</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米汽车广东省广州市番禺区番禺万达</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号</t>
+          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市番禺区番禺万达</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
+          <t>前进街道黄埔大道东663号</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区顺园路88-30号</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>江苏省常州市新北区顺园路88-30号</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>新城路668号</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区新城路授权服务中心</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>新城路668号</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -13239,7 +13239,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市龙湾区龙湾万达广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区永定路1188号万达广场中庭</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>成都天府公园111体验店</t>
+          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
+          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
+          <t>成都天府公园111体验店</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
+          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16532,17 +16532,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16569,12 +16569,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16623,22 +16623,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,29 +16744,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,29 +16904,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16953,12 +16953,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,29 +17000,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -17108,17 +17108,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17140,17 +17140,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17263,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17359,22 +17359,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17391,22 +17391,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17524,17 +17524,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
@@ -17556,17 +17556,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎城购物公园负一层 KFC 门口</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>瑞鼎城购物公园负一层 KFC 门口</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>北京丰台区丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>北京丰台区丽泽龙湖一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,7 +11159,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽省合肥市庐阳区蒙城北路汽车城</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>安徽省合肥市庐阳区蒙城北路1111号合肥恒信汽车博览中A9号商铺</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东省济南市莱芜区茂业天地</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>茂业天地购物中心1楼</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市莱芜区茂业天地</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>茂业天地购物中心1楼</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
+          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>小米汽车服务中心(宁波万成路店)</t>
+          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江宁波市宁海县宁海西子国际</t>
+          <t>小米汽车浙江宁波市海曙区万成路服务中心</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>浙江省宁波市宁海县跃龙街道桃源中路 168 号</t>
+          <t>小米汽车服务中心(宁波万成路店)</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
+          <t>成都天府公园111体验店</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
+          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>成都天府公园111体验店</t>
+          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
+          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,29 +16520,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16628,17 +16628,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16793,12 +16793,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,29 +16904,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,29 +17000,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17135,22 +17135,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17396,17 +17396,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -17524,17 +17524,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,29 +17544,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,29 +17576,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市闵行区浦江欢乐颂</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>浦江欢乐颂F1</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市闵行区浦江欢乐颂</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>浦江欢乐颂F1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎城购物公园负一层 KFC 门口</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市盘龙区瑞鼎城</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>瑞鼎城购物公园负一层 KFC 门口</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区龙岗星河WORLD·COCO Park</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市龙岗区坂田街道五和大道与雅宝路交汇处星河WORLD·COCO Park购物中心二楼星巴克旁</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海环球港品牌体验店</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>上海陆家嘴中心品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海环球港品牌体验店</t>
+          <t>上海陆家嘴中心品牌体验店</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
+          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -16505,12 +16505,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16628,17 +16628,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17204,17 +17204,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17263,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17332,17 +17332,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17396,17 +17396,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -17551,22 +17551,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -17576,29 +17576,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 76%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市青浦区徐泾镇天空万科广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市青浦区天空万科广场汽车体验店</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 76%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10280,7 +10280,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米澎程上海市浦东新区世博天地体验店</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>世博天地L123铺位</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米澎程上海市浦东新区世博天地体验店</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>世博天地L123铺位</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丰科万达</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>丰科万达一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京丰台区丰科万达</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>丰科万达一层中庭</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京通州区通州万达</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>通州万达一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京通州区通州万达</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>通州万达一层中庭</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市新都区五龙山汽车园</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>五龙山路189号10栋（宝马与方程豹中间)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
+          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
+          <t>长江西路安徽名车广场1018号</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>小米汽车安徽省合肥市蜀山区长江西路销售服务中心</t>
+          <t>小米汽车安徽合肥肥西县合肥肥西旭辉CMALL</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>长江西路安徽名车广场1018号</t>
+          <t>合肥市肥西县翡翠路与派河大道交口西侧旭辉CMALL3号门中庭</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
+          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区盛泽天虹商场</t>
+          <t>乌盆港路150号</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
+          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>乌盆港路150号</t>
+          <t>江苏省苏州市吴江区盛泽天虹商场</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>中强光年一楼1号门</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市新密市中强光年城市广场</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>中强光年一楼1号门</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米汽车湖北省武汉市洪山区金地广场</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>团结大道1335号金地广场</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市洪山区金地广场</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>团结大道1335号金地广场</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>成都悠方购物中心</t>
+          <t>成都双流万达广场体验店</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
+          <t>四川省成都市东升街道星空路二段399号</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>成都双流万达广场体验店</t>
+          <t>成都悠方购物中心</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市东升街道星空路二段399号</t>
+          <t>四川省成都市高新区交子大道300号1层L161/L162铺位</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>上海环球港品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海环球港品牌体验店</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>成都天府公园111体验店</t>
+          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -15821,7 +15821,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
+          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>成都双流万达广场城市展厅YX-CX-CD-05</t>
+          <t>成都天府公园111体验店</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>四川省成都市双流区东升街道星空路二段399号1栋1层1号  YX-CX-CD-05</t>
+          <t>四川省成都市金牛区北三环路一段111号3号楼1层104号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16520,29 +16520,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -16564,17 +16564,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16633,12 +16633,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16852,17 +16852,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>山东省潍坊市奎文区潍州路2800号 → 潍坊市奎文区潍州路金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店 → 宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,29 +17000,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -17044,17 +17044,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,29 +17096,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17135,22 +17135,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17172,17 +17172,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17268,17 +17268,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17300,17 +17300,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17327,22 +17327,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17391,22 +17391,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 82%</t>
         </is>
       </c>
     </row>
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省南京市江宁区麒麟宝龙</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 82%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,29 +17512,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
@@ -17583,22 +17583,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260727_vs_20260803.xlsx
@@ -10312,7 +10312,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市徐汇区徐汇万科</t>
+          <t>小米汽车上海市嘉定区嘉亭荟</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>小米之家(徐汇区徐汇万科专卖店)</t>
+          <t>嘉亭荟生活广场</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区嘉亭荟</t>
+          <t>小米汽车上海市浦东新区临港万达</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>嘉亭荟生活广场</t>
+          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区临港万达</t>
+          <t>小米汽车上海市徐汇区徐汇万科</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区中国(上海)自由贸易试验区临港新片区鸿音路2555号1层JY-BX-105门口</t>
+          <t>小米之家(徐汇区徐汇万科专卖店)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
+          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>都市车迷汽车城内（近南门出入口）</t>
+          <t>国际汽车城D07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>小米汽车云南省昆明市官渡区经开汽车城</t>
+          <t>小米汽车云南省昆明市盘龙区都市车迷智能汽车广场</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>国际汽车城D07</t>
+          <t>都市车迷汽车城内（近南门出入口）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京昌平区昌平悦荟</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>大兴龙湖天街一层中庭</t>
+          <t>昌平悦荟一层中庭</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京昌平区昌平悦荟</t>
+          <t>小米汽车北京市门头沟区长安龙湖天街</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>昌平悦荟一层中庭</t>
+          <t>北京市门头沟区长安龙湖天街一层</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>小米汽车北京市门头沟区长安龙湖天街</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市门头沟区长安龙湖天街一层</t>
+          <t>大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260525~20260622，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
+          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市新都区苏宁广场</t>
+          <t>小米汽车四川省成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>苏宁广场B口大堂（必胜客门口）</t>
+          <t>四川省成都市双流区双楠大道中段666号1栋5单元1层15031号</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
+          <t>小米汽车四川省成都市新都区苏宁广场</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>麓山大道二段1321号</t>
+          <t>苏宁广场B口大堂（必胜客门口）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市双流区万达广场</t>
+          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>双流万达一楼中庭近（大疆无人机店）</t>
+          <t>龙湖·滨江天街A馆-1F-03/04</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>小米澎程四川省成都市成华区龙湖滨江天街体验店</t>
+          <t>小米汽车四川省成都市双流区天府麓山汽车园</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>龙湖·滨江天街A馆-1F-03/04</t>
+          <t>麓山大道二段1321号</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都市青羊区天府今站购物中心</t>
+          <t>小米汽车四川省成都市双流区万达广场</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>天府广场今站购物中心负一楼（地铁天府广场站C口旁）</t>
+          <t>双流万达一楼中庭近（大疆无人机店）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市莱芜区茂业天地</t>
+          <t>小米汽车山东省济南市历城区经十路</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>茂业天地购物中心1楼</t>
+          <t>山东省济南市经十东路30766号力诺科技园</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东济南章丘区章丘世茂广场</t>
+          <t>小米汽车山东省济南市莱芜区茂业天地</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>章丘世茂广场1楼中庭</t>
+          <t>茂业天地购物中心1楼</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省济南市历城区经十路</t>
+          <t>小米汽车山东济南章丘区章丘世茂广场</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市经十东路30766号力诺科技园</t>
+          <t>章丘世茂广场1楼中庭</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260608，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
+          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>江山中路118-2号丰田汽车旁</t>
+          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市高新区金茂览秀城</t>
+          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>青岛市城阳高新区华东路2号金茂览秀城1F</t>
+          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>小米汽车山东省青岛市胶州市胶州龙湖</t>
+          <t>小米汽车山东省青岛市黄岛区江山路汽车城</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>山东省青岛市胶州市海尔大道和香港路交汇处西北角胶州龙湖天街1楼中庭</t>
+          <t>江山中路118-2号丰田汽车旁</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市番禺区番禺万达</t>
+          <t>小米澎程广东省广州市天河区美林天地体验店</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
+          <t>前进街道黄埔大道东663号</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>小米澎程广东省广州市天河区美林天地体验店</t>
+          <t>小米汽车广东省广州市番禺区番禺万达</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>前进街道黄埔大道东663号</t>
+          <t>广东省广州市番禺区番禺万达广场1楼1号中庭</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市光明区万达广场</t>
+          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区万达广场</t>
+          <t>小米汽车广东省深圳市光明区万达广场</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
+          <t>广东省深圳市光明区光明大道6号深圳光明万达广场1号门一楼中庭（麦记牛奶公司餐饮店旁）</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市坪山区坪山益田假日</t>
+          <t>小米汽车广东省深圳市龙岗区万达广场</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕（坪山段）168 号深圳坪山益田假日世界L1中庭，H&amp;M与水云间中间区域</t>
+          <t>广东省深圳市龙岗区华南二道1号深圳龙岗万达广场1L中庭</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
+          <t>小米汽车江苏省常州市溧阳市上河城</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
+          <t>上河城F1层</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
+          <t>小米汽车江苏省常州市新北区飞龙吾悦广场</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>江苏省常州市新北区顺园路88-30号</t>
+          <t>江苏省常州市新北区飞龙吾悦广场1号门</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省常州市溧阳市上河城</t>
+          <t>小米汽车江苏省常州市新北区薛家汽车城</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>上河城F1层</t>
+          <t>江苏省常州市新北区顺园路88-30号</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
+          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>乌盆港路150号</t>
+          <t>江苏省苏州市吴江区盛泽天虹商场</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市吴江区盛泽天虹</t>
+          <t>小米汽车江苏苏州市吴中区尹山国际汽车城</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴江区盛泽天虹商场</t>
+          <t>乌盆港路150号</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
+          <t>小米汽车河南省郑州市二七区南三环</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>巩义豪布斯卡一楼</t>
+          <t>郑州威佳奕邦汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
+          <t>小米汽车河南郑州二七区二七万达</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -12791,12 +12791,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>开元路省汽贸中心北门1号</t>
+          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南省郑州市二七区南三环</t>
+          <t>小米汽车河南省郑州市巩义市正上豪布斯卡</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>郑州威佳奕邦汽车销售服务有限公司</t>
+          <t>巩义豪布斯卡一楼</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州二七区二七万达</t>
+          <t>小米汽车河南省郑州市惠济区省汽贸销售服务中心</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>大学南路8号二七万达广场一楼小米汽车展台</t>
+          <t>开元路省汽贸中心北门1号</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -13000,7 +13000,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
+          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江嘉兴市平湖市平湖吾悦</t>
+          <t>小米汽车浙江嘉兴市嘉善县嘉善银泰</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路 811 号</t>
+          <t>嘉兴市嘉善县嘉善银泰嘉善大道399号</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -13160,7 +13160,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州桐庐县银泰城</t>
+          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
+          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州市临安区华兴汽车城</t>
+          <t>小米汽车浙江杭州桐庐县银泰城</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>浙江省杭州市临安区玲珑街道玲珑工业园区华兴汽车城 3 号厅</t>
+          <t>浙江省杭州市桐庐市环城南路555号1L中庭</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
+          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
+          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市永嘉县永嘉领悦广场</t>
+          <t>小米汽车浙江温州市乐清市柳市现代广场</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -13303,7 +13303,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>浙江省温州市永嘉县双塔路领悦广场1F中庭</t>
+          <t>浙江省温州市乐清市柳市镇扬帆路88号现代广场</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
+          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>湖北省武汉市硚口区园博大道1号</t>
+          <t>江夏永旺1F中庭</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市江夏区永旺梦乐城</t>
+          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>江夏永旺1F中庭</t>
+          <t>汉阳生活mall一楼Q1-8-1</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市汉阳区欧亚达商城</t>
+          <t>小米澎程湖北省武汉市硚口区武汉宜家荟聚体验店</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>汉阳生活mall一楼Q1-8-1</t>
+          <t>湖北省武汉市硚口区园博大道1号</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>小米汽车福建省厦门市同安区同安爱情海</t>
+          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
+          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -13768,7 +13768,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>小米澎程福建省厦门市湖里区湾悦城体验店</t>
+          <t>小米汽车福建省厦门市同安区同安爱情海</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -13783,7 +13783,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>日圆二里1号湾悦城L1-033A/033B/033C/035E</t>
+          <t>厦门市同安区智谷三路同安爱琴海购物中心</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>小米汽车重庆巴南区巴南万达</t>
+          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -14135,12 +14135,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>重庆巴南万达1F中庭</t>
+          <t>小米汽车(重庆光环购物公园体验店)</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>小米之家重庆市两江新区光环购物公园汽车体验店</t>
+          <t>小米汽车重庆巴南区巴南万达</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -14167,12 +14167,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>小米汽车(重庆光环购物公园体验店)</t>
+          <t>重庆巴南万达1F中庭</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260629，疑似此前漏爬）</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
+          <t>小米汽车黑龙江哈尔滨市西城红场</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>先锋路99号</t>
+          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>小米汽车黑龙江哈尔滨市西城红场</t>
+          <t>小米汽车黑龙江省哈尔滨市道外区先锋路销售服务中心</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市南岗区西城红场2号门小米之家门口</t>
+          <t>先锋路99号</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>上海环贸品牌体验店</t>
+          <t>上海陆家嘴中心品牌体验店</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -15629,7 +15629,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
+          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>上海环球港品牌体验店</t>
+          <t>上海环贸品牌体验店</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
+          <t>上海市徐汇区淮海中路999号环贸L1-167</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上海陆家嘴中心品牌体验店</t>
+          <t>上海环球港品牌体验店</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>上海市浦东区浦东南路 877 号、879 号、889 号、897 号、899 号上海陆家嘴中心商场第1层123商铺</t>
+          <t>上海市普陀区中山北路3300号环球港L1层L1150-1153店铺</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -16527,22 +16527,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
+          <t>南通金宝行汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
+          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
         </is>
       </c>
     </row>
@@ -16569,12 +16569,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -16584,7 +16584,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
         </is>
       </c>
     </row>
@@ -16596,17 +16596,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
+          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
         </is>
       </c>
     </row>
@@ -16628,17 +16628,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车漯河107国道销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
+          <t>榆阳区产业四路与青云二路交汇处 → 陕西省榆林市榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -16660,17 +16660,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车洛阳704青创园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
+          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
         </is>
       </c>
     </row>
@@ -16692,17 +16692,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津华北汽车城销售中心</t>
+          <t>小鹏汽车漯河107国道销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
+          <t>河南省漯河市源汇区梅花山路与桂江路交叉口向南路东67号 → 河南省漯河市源汇区桂江路与梅花山路交叉口向南路东67号</t>
         </is>
       </c>
     </row>
@@ -16724,17 +16724,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车天津华北汽车城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
+          <t>天津市北辰区津围公路15号华北创新产业园内 → 天津市北辰区宜兴埠镇津围公路15号院内东侧库区7-1号</t>
         </is>
       </c>
     </row>
@@ -16756,17 +16756,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅</t>
+          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
         </is>
       </c>
     </row>
@@ -16788,17 +16788,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊路与建材路交叉口西南300米 → 河南省周口市川汇区太昊西路40号</t>
+          <t>河北省张家口市胜利南路105号 → 河北省张家口市经济技术开发区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -16820,17 +16820,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区天一广场药行街 88 号 → 浙江省宁波市海曙区天一广场药行街88号</t>
+          <t>甘肃省张掖市甘州区绿舟汽车城内2号楼 → 甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层</t>
         </is>
       </c>
     </row>
@@ -16884,17 +16884,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
+          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
         </is>
       </c>
     </row>
@@ -16916,17 +16916,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车洛阳704青创园销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河南省洛阳市涧西区建设路152号东方红· 704青创产业园 → 河南省洛阳市涧西区建设路152号，东方红·704青创产业园</t>
+          <t>鄂尔多斯市康巴什区碳中和研究院内小鹏汽车 → 内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心</t>
         </is>
       </c>
     </row>
@@ -16948,17 +16948,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海杨浦销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
+          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
         </is>
       </c>
     </row>
@@ -16980,17 +16980,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车徐州高新汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -17000,29 +17000,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>徐州市铜山区珠江路汽车产业园华夏路28-7号 → 江苏省徐州市高新区珠江路汽车产业园华夏路28-7号</t>
+          <t>甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号 → 甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>南通金宝行汽车销售服务有限公司</t>
+          <t>小鹏汽车上海杨浦销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -17032,29 +17032,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>南通市通州区金沙街道石江公路5111号 → 江苏省南通市经济技术开发区驰程路5号</t>
+          <t>上海市杨浦区军工路1599号2至5幢 → 上海市杨浦区军工路1599号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售中心</t>
+          <t>小米之家上海市浦东新区世博天地汽车体验店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
+          <t>世博大道1515号 → 小米之家(浦东新区世博天地汽车体验店)</t>
         </is>
       </c>
     </row>
@@ -17076,17 +17076,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧） → 宝鸡市渭滨区高新十二路19号</t>
+          <t>河南省周口市川汇区太清路万国车世界一楼 → 河南省周口市川汇区万国车世界1楼</t>
         </is>
       </c>
     </row>
@@ -17108,17 +17108,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
+          <t>小米汽车山东省济宁市任城区万达广场</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -17140,17 +17140,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市平桥区南京大道</t>
+          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -17167,22 +17167,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋城万达）</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•晋城万达</t>
+          <t>小米汽车河南省信阳市平桥区南京大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -17199,22 +17199,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店</t>
+          <t>小米之家安徽省阜阳市颍州区万达汽车体验专卖店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨西城红场体验店F1B-08</t>
+          <t>小米之家安徽省阜阳市颍州区颍州万达汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -17231,22 +17231,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州平阳县平阳万达</t>
+          <t>惠州保时捷中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市平阳县平阳万达</t>
+          <t>惠州保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -17263,22 +17263,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
+          <t>华为智能生活馆•泉州晋江SM广场</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津市西青区大寺销售服务中心</t>
+          <t>华为授权体验店（晋江SM广场）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -17295,22 +17295,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>华为授权体验店（晋城万达）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区万达广场</t>
+          <t>华为智能生活馆•晋城万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -17327,22 +17327,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷中心</t>
+          <t>哈尔滨西城红场体验店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>惠州保时捷认可易手车及售后服务中心</t>
+          <t>哈尔滨西城红场体验店F1B-08</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -17364,17 +17364,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车天津市西青区大寺汽车园零售中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云冈区庞大汽贸园服务中心</t>
+          <t>小米汽车天津市西青区大寺销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -17391,22 +17391,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为智能生活馆•泉州晋江SM广场</t>
+          <t>小米汽车浙江温州平阳县平阳万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（晋江SM广场）</t>
+          <t>小米汽车浙江省温州市平阳县平阳万达</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -17460,17 +17460,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
+          <t>小米汽车上海市浦东新区复地活力城</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 74%</t>
+          <t>地址相似度 67%</t>
         </is>
       </c>
     </row>
@@ -17492,17 +17492,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市浦东新区复地活力城汽车体验店</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市浦东新区复地活力城</t>
+          <t>小米汽车山西省太原市万柏林区新城吾悦</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -17512,29 +17512,29 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 67%</t>
+          <t>地址相似度 74%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
+          <t>小米汽车河南漯河源汇区漯河万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
+          <t>小米汽车河南省漯河市源汇区万达广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 100%</t>
+          <t>店名相似度 81%</t>
         </is>
       </c>
     </row>
@@ -17583,22 +17583,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南漯河源汇区漯河万达</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-29</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省漯河市源汇区万达广场</t>
+          <t>重庆龙湖礼嘉天街城市展厅A-1F-37</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 81%</t>
+          <t>店名相似度 100%</t>
         </is>
       </c>
     </row>
